--- a/California_ECE_District_Contacts_2026-04-01.xlsx
+++ b/California_ECE_District_Contacts_2026-04-01.xlsx
@@ -72,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -90,6 +90,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -457,26 +463,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q53"/>
+  <dimension ref="A1:Q97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
-    <col width="44" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="72" customWidth="1" min="15" max="15"/>
-    <col width="46" customWidth="1" min="16" max="16"/>
-    <col width="72" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="29" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -4184,6 +4190,3028 @@
       <c r="Q53" s="6" t="inlineStr">
         <is>
           <t>Dr. Celia Munguia has focused PreK-3 responsibility under 'Strong Start' framing. Email not confirmed — check rowlandschools.org directory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Kern County Office of Education</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>0691012</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Kern</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>2054</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>1300 17th Street, Bakersfield, CA 93301</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr"/>
+      <c r="I54" s="3" t="inlineStr"/>
+      <c r="J54" s="3" t="inlineStr"/>
+      <c r="K54" s="3" t="inlineStr"/>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>(661) 861-6566</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr"/>
+      <c r="N54" s="3" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26; KCOE operates 13 child development centers | kern.org | 2024
+Expansion | Universal PreK expansion initiative underway | kern.org/early-childhood-education | 2024</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>https://kern.org/early-childhood-education/</t>
+        </is>
+      </c>
+      <c r="Q54" s="4" t="inlineStr">
+        <is>
+          <t>KCOE operates 13 child development centers serving 1,000+ preschoolers. Specific ECE director name not found in public directories. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Anaheim Elementary School District</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>0602610</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>14371</v>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>1001 South East Street, Anaheim, CA 92805</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>Office of Early Childhood Education (Director TBD)</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr"/>
+      <c r="K55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>(714) 517-7500</t>
+        </is>
+      </c>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>e2STEAM-D curriculum framework; AESD Learning Link program</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr"/>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2022
+Program | California State Preschool Program (CSPP) partnership with comprehensive preschool services expansion | anaheimelementary.org | 2024</t>
+        </is>
+      </c>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>https://anaheimelementary.org/ece/</t>
+        </is>
+      </c>
+      <c r="Q55" s="8" t="inlineStr">
+        <is>
+          <t>AESD ECE office located at 2000 W. Ball Rd. Director name not confirmed. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Fullerton School District</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>0614730</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>11262</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>1401 West Valencia Drive, Fullerton, CA 92833</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>Emily</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>McDougall</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>Director III, Educational Services (Preschool Program Director)</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>emily_mcdougall@myfsd.org</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>(714) 447-2878</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>California Preschool/Transitional Kindergarten Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26; expanding TK compliance per CA Ed Code 48000 | Fullerton School District | 2025</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fullertonsd.org/departments/educational-services/</t>
+        </is>
+      </c>
+      <c r="Q56" s="4" t="inlineStr">
+        <is>
+          <t>All 20 Fullerton schools recognized as Apple Distinguished Schools 2025-2028. Strong ECE program expansion underway for UTK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Santa Barbara Unified School District</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>0601414</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>Santa Barbara</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>13336</v>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>720 Santa Barbara Street, Santa Barbara, CA 93101</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>Maggie</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>Flores</t>
+        </is>
+      </c>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>Early Education Director</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>mflores@sbunified.org</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>(805) 963-8685</t>
+        </is>
+      </c>
+      <c r="M57" s="7" t="inlineStr">
+        <is>
+          <t>Developmentally appropriate, play-based curriculum aligned with Transitional Kindergarten</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr"/>
+      <c r="O57" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26; district adding new TK classrooms | sbunified.org | 2025
+Expansion | New TK classrooms opening including DLI program at McKinley Elementary; recurring UTK cost $1.27M/yr | The Santa Barbara Independent | Feb 2025</t>
+        </is>
+      </c>
+      <c r="P57" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sbunified.org/departments/educational-services/preschool-early-education</t>
+        </is>
+      </c>
+      <c r="Q57" s="8" t="inlineStr">
+        <is>
+          <t>District facing significant financial impact from UTK mandate. Email confirmed as Mflores@sbunified.org on district website — standardized to lowercase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Riverside County Office of Education</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>0691026</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>13942</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>3939 13th Street, Riverside, CA 92502</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>Joseph</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>M. Nieto III</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>Executive Director, Early Education Programs</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>jnieto@rcoe.us</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>(951) 826-6464</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>California Preschool Learning Foundations; play-based, developmentally appropriate</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2022
+Credential | New PK-3 ECE teaching credential approved at RCOE supporting workforce expansion | Commission on Teacher Credentialing | 2025
+PD | Bilingual by Design training offered at Excellence Through Education Conference 2025 | rcoe.us | 2025</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rcoe.us/departments/early-education-services/early-education-programs</t>
+        </is>
+      </c>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t>RCOE operates Early Learning and Literacy Project (RCELLP) supporting ages 2-5. New PK-3 credential program directly supports UTK expansion workforce needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Sunnyvale School District</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>0638460</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>5764</v>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>819 West Iowa Avenue, Sunnyvale, CA 94088</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr"/>
+      <c r="I59" s="7" t="inlineStr"/>
+      <c r="J59" s="7" t="inlineStr"/>
+      <c r="K59" s="7" t="inlineStr"/>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>(408) 522-8213</t>
+        </is>
+      </c>
+      <c r="M59" s="7" t="inlineStr">
+        <is>
+          <t>California Preschool/TK Learning Foundations; research-based best practices</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr"/>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2022</t>
+        </is>
+      </c>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sesd.org/about-usnew/departments/preschool</t>
+        </is>
+      </c>
+      <c r="Q59" s="8" t="inlineStr">
+        <is>
+          <t>Preschool office at Lakewood Elementary, Room 3, 750 Lakechime Drive. Offers state-funded and parent-pay programs. ECE director not identified — Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Bellflower Unified School District</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>0604440</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>9813</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>16703 South Clark Avenue, Bellflower, CA 90706</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>Bonnie</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Carter</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>Assistant Superintendent, Instruction and Student Support Services</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>iss@busd.k12.ca.us</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>(562) 866-9011</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Language-rich, play-based curriculum; Dual Immersion State Preschool available</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr"/>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2022
+Expansion | Dual Immersion State Preschool program active at ILC and Washington schools | busd.k12.ca.us | 2025</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>https://www.busd.k12.ca.us/programs/early-childhood-education</t>
+        </is>
+      </c>
+      <c r="Q60" s="4" t="inlineStr">
+        <is>
+          <t>ECE Office at 9301 Flower Street, Bellflower, CA 90706. No dedicated ECE Director; program overseen by Assistant Superintendent. Email listed is department inbox, not personal direct line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Placentia-Yorba Linda Unified School District</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>0630660</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>22698</v>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>1301 East Orangethorpe Avenue, Placentia, CA 92870</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="inlineStr">
+        <is>
+          <t>Sylvia</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>Cuesta</t>
+        </is>
+      </c>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
+          <t>Director II, Early Childhood Education</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>scuesta@pylusd.org</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>(714) 985-8652</t>
+        </is>
+      </c>
+      <c r="M61" s="7" t="inlineStr">
+        <is>
+          <t>Reggio Emilia philosophy; California Early Learning Foundations; play-based, inquiry-driven</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr"/>
+      <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2022
+Expansion | Bryant Ranch Preschool Program opened in Yorba Linda with Reggio Emilia play-based approach | pylusd.org | 2024</t>
+        </is>
+      </c>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>https://www.pylusd.org/apps/pages/child-development-services</t>
+        </is>
+      </c>
+      <c r="Q61" s="8" t="inlineStr">
+        <is>
+          <t>Email inferred from district pattern (first initial + last name). District has 34 sites with 5 state preschools. Confirm email via Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Palo Alto Unified School District</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>0629610</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>10209</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>25 Churchill Avenue, Palo Alto, CA 94306</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>Amanda</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Boyce</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>Director, Student Services (oversees Special Education PreK/ECE programs)</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>aboyce@pausd.org</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>(650) 329-3700</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>California Preschool/TK Learning Foundations; play-based and developmentally appropriate</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr"/>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2022
+Curriculum Review | District conducting comprehensive review of early childhood programs to assess effectiveness | pausd.org | 2025</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pausd.org/about-us/committees-task-forces/adhoc-committees/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q62" s="4" t="inlineStr">
+        <is>
+          <t>Amanda Boyce oversees TK, Special Ed Preschool, and PreSchool Family programs. TK programs at Barron Park, Duveneck, Fairmeadow, and Walter Hays elementary schools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>Turlock Unified School District</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>0600158</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>Stanislaus</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>13744</v>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>825 Sycamore Street, Turlock, CA 95380</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>Judy</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>Huerta</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>Director, Early Childhood Education</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>jhuerta@turlock.k12.ca.us</t>
+        </is>
+      </c>
+      <c r="K63" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L63" s="7" t="inlineStr">
+        <is>
+          <t>(209) 632-2857</t>
+        </is>
+      </c>
+      <c r="M63" s="7" t="inlineStr">
+        <is>
+          <t>California State Preschool Program (CSPP) and Head Start; school readiness focus</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr"/>
+      <c r="O63" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2022</t>
+        </is>
+      </c>
+      <c r="P63" s="7" t="inlineStr">
+        <is>
+          <t>https://www.turlock.k12.ca.us/schools/early-childhood-education-staff</t>
+        </is>
+      </c>
+      <c r="Q63" s="8" t="inlineStr">
+        <is>
+          <t>Programs at 4 elementary campuses serving 400+ children ages 3-5. State Preschool and Head Start both available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Cupertino Union School District</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>0610290</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>13533</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>10301 Vista Drive, Cupertino, CA 95014</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr"/>
+      <c r="I64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr"/>
+      <c r="K64" s="3" t="inlineStr"/>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>(408) 252-3000</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>CuperDoodle Preschool program — play-based, hands-on; cognitive, social-emotional, physical development</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="O64" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2022
+Expansion | CuperDoodle preschool expanded from John Muir Elementary to Montclaire | cusdk8.org | 2024</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>https://cuperdoodle.cusdk8.org/</t>
+        </is>
+      </c>
+      <c r="Q64" s="4" t="inlineStr">
+        <is>
+          <t>CuperDoodle launched 2018; accepts ages 2.9-6. ECE director not publicly listed — check cusdk8.org/staff. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Livermore Valley Joint Unified School District</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>0622110</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="n">
+        <v>12968</v>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>685 East Jack London Boulevard, Livermore, CA 94551</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr"/>
+      <c r="H65" s="7" t="inlineStr"/>
+      <c r="I65" s="7" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr"/>
+      <c r="K65" s="7" t="inlineStr"/>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>(925) 606-3238</t>
+        </is>
+      </c>
+      <c r="M65" s="7" t="inlineStr">
+        <is>
+          <t>TK play-based, hands-on curriculum; social-emotional, science, literacy, math, motor skills focus</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr"/>
+      <c r="O65" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK — LVJUSD welcoming all children turning 4 by Sept 1 2025 for UTK 2025-26 | livermoreschools.org | 2025</t>
+        </is>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>https://www.livermoreschools.org/departments/curriculum-instruction/transitional-kindergarten</t>
+        </is>
+      </c>
+      <c r="Q65" s="8" t="inlineStr">
+        <is>
+          <t>TK available at all elementary and K-8 schools, 8:30 AM - 1:30 PM daily. ECE director not publicly listed. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Monterey Peninsula Unified School District</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>0625530</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Monterey</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>9400</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>700 Hilby Avenue, Seaside, CA 93955</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr"/>
+      <c r="I66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr"/>
+      <c r="K66" s="3" t="inlineStr"/>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>(831) 645-1272</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>Play- and story-based curriculum; social-emotional, language development, multicultural, music and arts</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr"/>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2022
+Expansion | MPUSD opened new preschool at Monterey CDC; operates Marina and Seaside Child Development Centers | preschool.mpusd.net | 2024</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>https://preschool.mpusd.net/</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="inlineStr">
+        <is>
+          <t>4 preschool programs: Dual Language Academy, Marina CDC, Monterey CDC, Seaside CDC. Sliding scale tuition. ECE director not publicly listed — Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>San Mateo-Foster City Elementary School District</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>0634920</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>San Mateo</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>9926</v>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>1170 Chess Drive, Foster City, CA 94404</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr"/>
+      <c r="H67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr"/>
+      <c r="J67" s="7" t="inlineStr"/>
+      <c r="K67" s="7" t="inlineStr"/>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>(650) 312-7700</t>
+        </is>
+      </c>
+      <c r="M67" s="7" t="inlineStr">
+        <is>
+          <t>California Preschool Learning Foundations; play-based; Montessori, Spanish immersion, Mandarin immersion options</t>
+        </is>
+      </c>
+      <c r="N67" s="7" t="inlineStr"/>
+      <c r="O67" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2022
+Expansion | Preschool enrollment surged 300% (164 to 541 students); 8 new classrooms established | smfcsd.net | 2024</t>
+        </is>
+      </c>
+      <c r="P67" s="7" t="inlineStr">
+        <is>
+          <t>https://www.smfcsd.net/district-departments/student-services/preschool-program</t>
+        </is>
+      </c>
+      <c r="Q67" s="8" t="inlineStr">
+        <is>
+          <t>7 CSPP-funded classrooms + 1 fee-based; specialized Montessori, Spanish immersion, Mandarin immersion programs. ECE director not publicly listed — Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Alameda Unified School District</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>0601770</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>10771</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>2060 Challenger Drive, Alameda, CA 94501</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>Jill</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Hunter</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>Coordinator of Early Childhood Education</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>jhunter@alamedaunified.org</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>(510) 337-7000</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Woodstock Child Development Center (WCDC) program; ages 18 months through grade 3</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr"/>
+      <c r="O68" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2022
+Leadership | Jill Hunter appointed new Coordinator of Early Childhood Education Feb 2024 — new decision-maker window | AUSD Board | Feb 2024</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>https://wcdc.alamedaunified.org/</t>
+        </is>
+      </c>
+      <c r="Q68" s="4" t="inlineStr">
+        <is>
+          <t>Jill Hunter transitioned from Program Manager, Preschool and Elementary Special Education. Also oversees Ardella Dailey Special Ed Preschool. WCDC established 1943; year-round 7am-5:45pm M-F.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Berkeley Unified School District</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>0604740</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>Alameda</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>9872</v>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>2020 Bonar Street, Berkeley, CA 94702</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr"/>
+      <c r="H69" s="7" t="inlineStr"/>
+      <c r="I69" s="7" t="inlineStr"/>
+      <c r="J69" s="7" t="inlineStr"/>
+      <c r="K69" s="7" t="inlineStr"/>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>(510) 644-6150</t>
+        </is>
+      </c>
+      <c r="M69" s="7" t="inlineStr">
+        <is>
+          <t>California Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="inlineStr"/>
+      <c r="O69" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2022
+Expansion | BUSD expanding TK program from partial to full UTK implementation | berkeleyschools.net | 2023</t>
+        </is>
+      </c>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>https://berkeleyschools.net/schools/early-childhood-education/</t>
+        </is>
+      </c>
+      <c r="Q69" s="8" t="inlineStr">
+        <is>
+          <t>ECE director name not identified. Recommend contacting ECE department directly. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Huntington Beach City School District</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>0618030</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>4624</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>19231 Harding Lane, Huntington Beach, CA 92646</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Rochelle</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>Director of Early Childhood Education</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr"/>
+      <c r="K70" s="3" t="inlineStr"/>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>(714) 378-2033</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>California Preschool Learning Foundations; GLAD (Guided Language Acquisition Design)</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr"/>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Curriculum | GLAD instructional model adopted for ECE programs | hbcsd.k12.ca.us | 2024</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hbcsd.k12.ca.us/11601_3</t>
+        </is>
+      </c>
+      <c r="Q70" s="4" t="inlineStr">
+        <is>
+          <t>19 years ECE experience; email not located despite confirmed name and title. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>Milpitas Unified School District</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>0624500</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>10086</v>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>1331 East Calaveras Boulevard, Milpitas, CA 95035</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>Arti</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Sharma</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>Coordinator of Early Childhood Development and Community Engagement</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>asharma@musd.org</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>(408) 635-2600</t>
+        </is>
+      </c>
+      <c r="M71" s="7" t="inlineStr">
+        <is>
+          <t>Children's Progress Academic Assessment (CPAA) Pre-K; California Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N71" s="7" t="inlineStr"/>
+      <c r="O71" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Curriculum Review | District maintains active curriculum adoption process | musd.org | 2024</t>
+        </is>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>https://www.musd.org/31614_2</t>
+        </is>
+      </c>
+      <c r="Q71" s="8" t="inlineStr">
+        <is>
+          <t>High-confidence contact with email confirmed on official MUSD Learning and Development page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Napa Valley Unified School District</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>0626640</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Napa</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>16381</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>2425 Jefferson Street, Napa, CA 94559</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
+        <is>
+          <t>Yasmin</t>
+        </is>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Rahimtoola</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Special Education Coordinator (Early Childhood)</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>yasmin_rahimtoola@nvusd.org</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr"/>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>State Preschool Program; California Preschool Learning Foundations</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr"/>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nvusd.org/our-schools/early-childhood-special-education</t>
+        </is>
+      </c>
+      <c r="Q72" s="4" t="inlineStr">
+        <is>
+          <t>Yasmin Rahimtoola focus is early childhood special education ages 3-5. Confirm whether she also oversees general ECE curriculum decisions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>Novato Unified School District</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>0627720</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Marin</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>7516</v>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>901 Rowland Boulevard, Novato, CA 94945</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>Lynzie</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Brodhun</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>Director of PK-8 Educational Services</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>lbrodhun@nusd.org</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+      <c r="N73" s="7" t="inlineStr"/>
+      <c r="O73" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Leadership | Lynzie Brodhun appointed Director of PK-8 Educational Services effective July 1 2024 — new decision-maker | edcal.acsa.org | Jun 2024</t>
+        </is>
+      </c>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t>https://www.nusd.org/271395_2?personID=334038</t>
+        </is>
+      </c>
+      <c r="Q73" s="8" t="inlineStr">
+        <is>
+          <t>Brodhun appointed effective July 1, 2024; oversees all early childhood programs. New leadership = open window. Curriculum program not yet identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Gilroy Unified School District</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>0615180</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>10200</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>245 Farrell Avenue, Gilroy, CA 95020</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Beatrice</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Magdaleno</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>Program Administrator for Early Childhood Education</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>beatrice.magdaleno@gilroyunified.org</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>(669) 205-7960</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>State Preschool Program; Dual Immersion Preschool (90:10 Spanish/English model)</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr"/>
+      <c r="O74" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Expansion | Dual immersion preschool at Glen View State Preschool with 90:10 language model | gilroyunified.org | 2024</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gilroyunified.org/departments/educational-services/early-childhood-education</t>
+        </is>
+      </c>
+      <c r="Q74" s="4" t="inlineStr">
+        <is>
+          <t>Email verified on official ECE page. Preschool Office maintains 3 locations including dual immersion program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Morgan Hill Unified School District</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>0625830</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>8483</v>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>15600 Concord Circle, Morgan Hill, CA 95037</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr"/>
+      <c r="H75" s="7" t="inlineStr"/>
+      <c r="I75" s="7" t="inlineStr"/>
+      <c r="J75" s="7" t="inlineStr"/>
+      <c r="K75" s="7" t="inlineStr"/>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>(408) 201-6023</t>
+        </is>
+      </c>
+      <c r="M75" s="7" t="inlineStr"/>
+      <c r="N75" s="7" t="inlineStr"/>
+      <c r="O75" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>https://www.mhusd.org/departments/educational-services</t>
+        </is>
+      </c>
+      <c r="Q75" s="8" t="inlineStr">
+        <is>
+          <t>ECE director contact not located. District has Special Education Preschool. Recommend contacting Educational Services dept. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Cajon Valley Union School District</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>0606810</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>15607</v>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>750 East Main Street, El Cajon, CA 92020</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr"/>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>Director of Early Childhood Education (position identified, name not confirmed)</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr"/>
+      <c r="K76" s="3" t="inlineStr"/>
+      <c r="L76" s="3" t="inlineStr"/>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>JumpStart! Program; California State Preschool Program; Transitional Kindergarten</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr"/>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Expansion | Multiple free and fee-based preschool programs including Special Ed PreK | cajonvalley.net | 2024</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cajonvalley.net/Page/17967</t>
+        </is>
+      </c>
+      <c r="Q76" s="4" t="inlineStr">
+        <is>
+          <t>Director position exists per job descriptions but specific name not confirmed. Contact through Educational Services or Personnel Services depts. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Hemet Unified School District</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>0616920</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Riverside</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>22891</v>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>1791 West Acacia Avenue, Hemet, CA 92545</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>Alice</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Chung</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>Principal, Hemet Preschool</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr"/>
+      <c r="K77" s="7" t="inlineStr"/>
+      <c r="L77" s="7" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr">
+        <is>
+          <t>State Preschool Program; Early Childhood Special Education</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr"/>
+      <c r="O77" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P77" s="7" t="inlineStr">
+        <is>
+          <t>https://preschool.hemetusd.org/</t>
+        </is>
+      </c>
+      <c r="Q77" s="8" t="inlineStr">
+        <is>
+          <t>Alice Chung confirmed as Hemet Preschool Principal. Email not located. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>King City Union School District</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>0619680</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Monterey</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>2552</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>104 South Vanderhurst Avenue, King City, CA 93930</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr"/>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="3" t="inlineStr"/>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>(831) 385-2940</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>Dual Language Immersion Program (TK-1st grade) at Santa Lucia Elementary</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr"/>
+      <c r="O78" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025
+Program | Dual language immersion program PreK-8 | kcusd.org | 2024</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>https://kcusd.org/en-US/staff</t>
+        </is>
+      </c>
+      <c r="Q78" s="4" t="inlineStr">
+        <is>
+          <t>Small district serving PreK-8. ECE director not identified. Recommend calling main office. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles County Office of Education</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>1910199</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>1597</v>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>9300 East Imperial Highway, Downey, CA 90242</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>AnnMarie</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>District Intern Instructor, Supervisor, and PK-3 Coordinator</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>smith_annmarie@lacoe.edu</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>(562) 940-1868</t>
+        </is>
+      </c>
+      <c r="M79" s="7" t="inlineStr">
+        <is>
+          <t>California Early Learning Foundations; PK-3 ECE Specialist Instruction Credential program</t>
+        </is>
+      </c>
+      <c r="N79" s="7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="O79" s="8" t="inlineStr">
+        <is>
+          <t>Credential | LACOE approved as provider for new PK-3 ECE District Intern Credential pathway April 2024 | lacoe.edu | Apr 2024
+Grant/Mandate | LACOE operates CA's largest Head Start-State Preschool; UTK expansion support to 81 LA County districts | lacoe.edu | 2024
+PD | TK teacher institutes, communities of practice, and UTK administrators institute offered | lacoe.edu | 2024</t>
+        </is>
+      </c>
+      <c r="P79" s="7" t="inlineStr">
+        <is>
+          <t>https://www.lacoe.edu/services/staff-support/credential-programs/beginning-teacher-programs/pk-3-early-childhood-education-specialist-instruction-credential</t>
+        </is>
+      </c>
+      <c r="Q79" s="8" t="inlineStr">
+        <is>
+          <t>LACOE directly serves ~1,597 students but provides services to 81 LA County districts and ~2M students. AnnMarie Smith confirmed as PK-3 Coordinator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>San Diego County Office of Education</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>0691030</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>6401 Linda Vista Road, San Diego, CA 92111</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr">
+        <is>
+          <t>Dr.</t>
+        </is>
+      </c>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>Rita Palet</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>Executive Director of Early Education Programs and Services</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr"/>
+      <c r="K80" s="3" t="inlineStr"/>
+      <c r="L80" s="3" t="inlineStr"/>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>Quality Preschool Initiative; ASPIRE Program for inclusive early learners</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr"/>
+      <c r="O80" s="4" t="inlineStr">
+        <is>
+          <t>Program | ASPIRE program launch — SDCOE selected to lead regional inclusive early education | sdcoe.net | 2024
+Grant | Child Care Workforce Investment grant for early education leaders and TA | sdcoe.net | 2024
+Program | San Diego Quality Preschool Initiative for program improvement | sdcoe.net | 2024</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sdcoe.net/special-populations/early-education</t>
+        </is>
+      </c>
+      <c r="Q80" s="4" t="inlineStr">
+        <is>
+          <t>Dr. Rita Palet confirmed as Executive Director. Email partially masked in public sources — recommend Apollo.io. SDCOE serves 43 districts and 480K+ county students.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>Orange County Department of Education</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr"/>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr"/>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>200 Kalmus Drive, Costa Mesa, CA 92626</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>Jonathan</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>Swanson</t>
+        </is>
+      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>Executive Director, Academic Content and Instructional Support (includes Early and Expanded Learning)</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr"/>
+      <c r="K81" s="7" t="inlineStr"/>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>(714) 327-1077</t>
+        </is>
+      </c>
+      <c r="M81" s="7" t="inlineStr">
+        <is>
+          <t>Early Education Programs (various state-funded initiatives)</t>
+        </is>
+      </c>
+      <c r="N81" s="7" t="inlineStr"/>
+      <c r="O81" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | OCDE supporting 28 districts with UTK mandate implementation 2025-26 | ocde.us | 2025
+Expansion | Early Education Programs serving county's youngest learners with expansion plans | ocde.us | 2024</t>
+        </is>
+      </c>
+      <c r="P81" s="7" t="inlineStr">
+        <is>
+          <t>https://ocde.us/EarlyEducation/Pages/default.aspx</t>
+        </is>
+      </c>
+      <c r="Q81" s="8" t="inlineStr">
+        <is>
+          <t>Jonathan Swanson oversees early education. Janice Howver (jhowver@ocde.us) also listed as ECE Coordinator — may be better direct contact. OCDE serves 28 districts and 600K+ students. Email needed for Swanson — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara County Office of Education</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>4310439</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Santa Clara</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr"/>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>1290 Ridder Road, San Jose, CA 95155</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr"/>
+      <c r="H82" s="3" t="inlineStr"/>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>Director III - Early Learning Services (position open as of early 2025)</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr"/>
+      <c r="K82" s="3" t="inlineStr"/>
+      <c r="L82" s="3" t="inlineStr"/>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>Head Start; State Preschool; Strong Start Coalition curriculum</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr"/>
+      <c r="O82" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | SCCOE supporting all 31 county districts with UTK 2025-26 implementation | sccoe.org | 2025
+Strategic | Strong Start Coalition expanding high-quality early learning access ages 0-8 across Santa Clara County | sccoe.org/strongstart | 2024
+Program | Quality Matters initiative to strengthen quality of early learning birth-8 | childcarescc.org | 2024</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sccoe.org/depts/educational-services/early-learning-services/Pages/home.aspx</t>
+        </is>
+      </c>
+      <c r="Q82" s="4" t="inlineStr">
+        <is>
+          <t>Director III - Early Learning Services position open as of early 2025 — leadership transition = open window. Serves 31 districts. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>Tulare County Office of Education</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr"/>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>Tulare</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr"/>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>7000 Doe Avenue, Suite C, Visalia, CA 93291</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="inlineStr"/>
+      <c r="H83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>Assistant Administrator, Early Childhood Education</t>
+        </is>
+      </c>
+      <c r="J83" s="7" t="inlineStr">
+        <is>
+          <t>ebarron@cc.tcoe.org</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>(559) 651-3026</t>
+        </is>
+      </c>
+      <c r="M83" s="7" t="inlineStr">
+        <is>
+          <t>Head Start; State Preschool; Early Head Start; Migrant Head Start programs</t>
+        </is>
+      </c>
+      <c r="N83" s="7" t="inlineStr"/>
+      <c r="O83" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | TCOE coordinating ECE programs across Tulare County for UTK mandate 2025-26 | tcoe.org | 2025
+Expansion | Currently enrolling for 2025-2026 ECE programs | tcoe.org/ECE | 2025</t>
+        </is>
+      </c>
+      <c r="P83" s="7" t="inlineStr">
+        <is>
+          <t>https://tcoe.org/ECE</t>
+        </is>
+      </c>
+      <c r="Q83" s="8" t="inlineStr">
+        <is>
+          <t>E. Barron listed as referral contact (ebarron@cc.tcoe.org). Specific director name not confirmed. Email is admin contact, not named director. Director name needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Fresno County Office of Education</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>0691018</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Fresno</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr"/>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>1111 Van Ness Avenue, Fresno, CA 93721</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr"/>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>Early Childhood Education Division</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr"/>
+      <c r="K84" s="3" t="inlineStr"/>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>(559) 265-3000</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>Head Start; State Preschool; California State Preschool Program</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr"/>
+      <c r="O84" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | FCOE supporting districts in Fresno County with UTK mandate 2025-26 | fcoe.org | 2025</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>https://www.fcoe.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q84" s="4" t="inlineStr">
+        <is>
+          <t>ECE director name not identified. Recommend contacting main office. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>Stanislaus County Office of Education</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>0691032</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>Stanislaus</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr"/>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>1100 H Street, Modesto, CA 95354</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>Tony</t>
+        </is>
+      </c>
+      <c r="H85" s="7" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>Executive Director, Child and Family Services</t>
+        </is>
+      </c>
+      <c r="J85" s="7" t="inlineStr"/>
+      <c r="K85" s="7" t="inlineStr"/>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>(209) 238-1800</t>
+        </is>
+      </c>
+      <c r="M85" s="7" t="inlineStr">
+        <is>
+          <t>Head Start; State Preschool; Child Development programs</t>
+        </is>
+      </c>
+      <c r="N85" s="7" t="inlineStr"/>
+      <c r="O85" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | SCOE supporting district UTK mandate implementation across Stanislaus County 2025-26 | scoe.net | 2025</t>
+        </is>
+      </c>
+      <c r="P85" s="7" t="inlineStr">
+        <is>
+          <t>https://www.scoe.net/departments/child-family</t>
+        </is>
+      </c>
+      <c r="Q85" s="8" t="inlineStr">
+        <is>
+          <t>Tony Jordan confirmed as Executive Director, Child and Family Services. Email not located — Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Butte County Office of Education</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>0691010</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Butte</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr"/>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>1859 Bird Street, Oroville, CA 95965</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>Lucero</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>Director, Early Childhood Education</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr"/>
+      <c r="K86" s="3" t="inlineStr"/>
+      <c r="L86" s="3" t="inlineStr"/>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>Head Start; State Preschool; Early Head Start</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr"/>
+      <c r="O86" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | BCOE supporting Butte County districts with UTK mandate 2025-26 | bcoe.org | 2025</t>
+        </is>
+      </c>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bcoe.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q86" s="4" t="inlineStr">
+        <is>
+          <t>Michelle Lucero confirmed as director. Email not located — Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
+        <is>
+          <t>San Bernardino County Superintendent of Schools</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="inlineStr">
+        <is>
+          <t>0691028</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>San Bernardino</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr"/>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>601 North E Street, San Bernardino, CA 92415</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>Heather</t>
+        </is>
+      </c>
+      <c r="H87" s="7" t="inlineStr">
+        <is>
+          <t>Smith</t>
+        </is>
+      </c>
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>Director, Early Education and Development</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
+        <is>
+          <t>heather.smith@sbcss.net</t>
+        </is>
+      </c>
+      <c r="K87" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L87" s="7" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr">
+        <is>
+          <t>Footsteps2Brilliance; Clever Kids University with Learn With Me multimedia series</t>
+        </is>
+      </c>
+      <c r="N87" s="7" t="inlineStr"/>
+      <c r="O87" s="8" t="inlineStr">
+        <is>
+          <t>Curriculum | Footsteps2Brilliance and Clever Kids University programs active in ECE | sbcss.net | 2024
+Grant/Mandate | SBCSS supporting county districts with UTK mandate 2025-26 | sbcss.net | 2025</t>
+        </is>
+      </c>
+      <c r="P87" s="7" t="inlineStr">
+        <is>
+          <t>https://www.sbcss.net/departments/early-education</t>
+        </is>
+      </c>
+      <c r="Q87" s="8" t="inlineStr">
+        <is>
+          <t>Heather Smith confirmed as Director, Early Education and Development. Serves all San Bernardino County districts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Vallejo City Unified School District</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>0640230</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Solano</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr"/>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>665 Walnut Avenue, Vallejo, CA 94592</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>Juli</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>Robbins</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>Director of Elementary Education</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>jrobbins@vcusd.org</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr"/>
+      <c r="M88" s="3" t="inlineStr"/>
+      <c r="N88" s="3" t="inlineStr"/>
+      <c r="O88" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P88" s="3" t="inlineStr">
+        <is>
+          <t>https://www.vcusd.org/departments/educational-services</t>
+        </is>
+      </c>
+      <c r="Q88" s="4" t="inlineStr">
+        <is>
+          <t>Juli Robbins confirmed as Director of Elementary Education overseeing ECE. Curriculum program not identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>Pittsburg Unified School District</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>0631260</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>Contra Costa</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr"/>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>2000 Railroad Avenue, Pittsburg, CA 94565</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr"/>
+      <c r="I89" s="7" t="inlineStr"/>
+      <c r="J89" s="7" t="inlineStr"/>
+      <c r="K89" s="7" t="inlineStr"/>
+      <c r="L89" s="7" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
+      <c r="N89" s="7" t="inlineStr"/>
+      <c r="O89" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P89" s="7" t="inlineStr">
+        <is>
+          <t>https://www.pittsburgusd.org</t>
+        </is>
+      </c>
+      <c r="Q89" s="8" t="inlineStr">
+        <is>
+          <t>ECE director not identified. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Vacaville Unified School District</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>0640170</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Solano</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr"/>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>751 School Street, Vacaville, CA 95688</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr"/>
+      <c r="H90" s="3" t="inlineStr"/>
+      <c r="I90" s="3" t="inlineStr"/>
+      <c r="J90" s="3" t="inlineStr"/>
+      <c r="K90" s="3" t="inlineStr"/>
+      <c r="L90" s="3" t="inlineStr"/>
+      <c r="M90" s="3" t="inlineStr"/>
+      <c r="N90" s="3" t="inlineStr"/>
+      <c r="O90" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P90" s="3" t="inlineStr">
+        <is>
+          <t>https://www.vacavilleusd.org</t>
+        </is>
+      </c>
+      <c r="Q90" s="4" t="inlineStr">
+        <is>
+          <t>ECE director not identified. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>Fairfield-Suisun Unified School District</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>0613920</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Solano</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>2490 Hilborn Road, Fairfield, CA 94534</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr"/>
+      <c r="I91" s="7" t="inlineStr"/>
+      <c r="J91" s="7" t="inlineStr"/>
+      <c r="K91" s="7" t="inlineStr"/>
+      <c r="L91" s="7" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
+      <c r="N91" s="7" t="inlineStr"/>
+      <c r="O91" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P91" s="7" t="inlineStr">
+        <is>
+          <t>https://www.fsusd.org</t>
+        </is>
+      </c>
+      <c r="Q91" s="8" t="inlineStr">
+        <is>
+          <t>ECE director not identified. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Downey Unified School District</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>0611520</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr"/>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>11627 Brookshire Avenue, Downey, CA 90241</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr"/>
+      <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr"/>
+      <c r="K92" s="3" t="inlineStr"/>
+      <c r="L92" s="3" t="inlineStr"/>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>Creative Curriculum for Preschool (Teaching Strategies)</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr"/>
+      <c r="O92" s="4" t="inlineStr">
+        <is>
+          <t>Curriculum | Creative Curriculum for Preschool confirmed in use | downeyusd.net | 2024
+Expansion | District launched LEAP program for 3-year-olds in 2024 | downeyusd.net | 2024
+Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P92" s="3" t="inlineStr">
+        <is>
+          <t>https://www.downeyusd.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q92" s="4" t="inlineStr">
+        <is>
+          <t>Creative Curriculum confirmed. LEAP (Learning through Exploration, Art, and Play) launched for 3-year-olds 2024. ECE director name not identified — Apollo.io needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>El Monte Union High School District</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>0612780</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr"/>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>3537 Johnson Avenue, El Monte, CA 91731</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr"/>
+      <c r="H93" s="7" t="inlineStr"/>
+      <c r="I93" s="7" t="inlineStr"/>
+      <c r="J93" s="7" t="inlineStr"/>
+      <c r="K93" s="7" t="inlineStr"/>
+      <c r="L93" s="7" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
+      <c r="N93" s="7" t="inlineStr"/>
+      <c r="O93" s="8" t="inlineStr"/>
+      <c r="P93" s="7" t="inlineStr">
+        <is>
+          <t>https://www.emuhsd.org</t>
+        </is>
+      </c>
+      <c r="Q93" s="8" t="inlineStr">
+        <is>
+          <t>HIGH SCHOOL district (grades 9-12 only). No PreK/ECE programs. Not a target for curriculum outreach. Included for completeness — deprioritize for outreach.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Pasadena Unified School District</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>0629370</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr"/>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>351 South Hudson Avenue, Pasadena, CA 91109</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>Lindsay</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>Lewis</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>Director of Early Childhood Education</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>lewis.lindsay@pusd.us</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr"/>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>Creative Curriculum (Teaching Strategies)</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="O94" s="4" t="inlineStr">
+        <is>
+          <t>Curriculum | Creative Curriculum (Teaching Strategies) in use since 2016 — long-standing user; potential renewal or upgrade opportunity | pusd.us | 2016
+Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.pusd.us/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q94" s="4" t="inlineStr">
+        <is>
+          <t>Lindsay Lewis confirmed as Director of Early Childhood Education. Creative Curriculum adopted 2016.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="7" t="inlineStr">
+        <is>
+          <t>Baldwin Park Unified School District</t>
+        </is>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>0603690</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr"/>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>3699 North Holly Avenue, Baldwin Park, CA 91706</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr"/>
+      <c r="K95" s="7" t="inlineStr"/>
+      <c r="L95" s="7" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr">
+        <is>
+          <t>Developmentally appropriate integrated curriculum with open-ended play; Early Head Start and Head Start</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr"/>
+      <c r="O95" s="8" t="inlineStr">
+        <is>
+          <t>Program | Long-standing Early Head Start and Head Start programs; strong ECE infrastructure | bpusd.net | 2024
+Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P95" s="7" t="inlineStr">
+        <is>
+          <t>https://www.bpusd.net/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q95" s="8" t="inlineStr">
+        <is>
+          <t>ECE director name not identified. Long-running Head Start program in place. Email needed — Apollo.io.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Redlands Unified School District</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>0632070</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>San Bernardino</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr"/>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>20 West Lugonia Avenue, Redlands, CA 92374</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>Denise</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>Fee</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>Director II, Educational Services</t>
+        </is>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>dfee@redlands.k12.ca.us</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr"/>
+      <c r="M96" s="3" t="inlineStr"/>
+      <c r="N96" s="3" t="inlineStr"/>
+      <c r="O96" s="4" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P96" s="3" t="inlineStr">
+        <is>
+          <t>https://www.redlandsusd.net/departments/educational-services</t>
+        </is>
+      </c>
+      <c r="Q96" s="4" t="inlineStr">
+        <is>
+          <t>Denise Fee confirmed as Director II overseeing Educational Services including ECE. Curriculum program not identified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Chico Unified School District</t>
+        </is>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>0608490</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>Butte</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr"/>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>1163 East Seventh Street, Chico, CA 95928</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>Cate</t>
+        </is>
+      </c>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>Szczepanski</t>
+        </is>
+      </c>
+      <c r="I97" s="7" t="inlineStr">
+        <is>
+          <t>Director, Early Childhood Education</t>
+        </is>
+      </c>
+      <c r="J97" s="7" t="inlineStr"/>
+      <c r="K97" s="7" t="inlineStr"/>
+      <c r="L97" s="7" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
+      <c r="N97" s="7" t="inlineStr"/>
+      <c r="O97" s="8" t="inlineStr">
+        <is>
+          <t>Grant/Mandate | California UTK mandate — all 4-yr-olds eligible TK 2025-26 | cde.ca.gov | 2025</t>
+        </is>
+      </c>
+      <c r="P97" s="7" t="inlineStr">
+        <is>
+          <t>https://www.chicousd.org/departments/early-childhood</t>
+        </is>
+      </c>
+      <c r="Q97" s="8" t="inlineStr">
+        <is>
+          <t>Cate Szczepanski confirmed as ECE director. Email not located — Apollo.io needed.</t>
         </is>
       </c>
     </row>
